--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{836F7BD3-B404-7B43-8549-05032A2B9A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCCA43B-3F56-0941-9A80-D2A9636FEC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Vinst</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>Marocko</t>
+  </si>
+  <si>
+    <t>Norge</t>
+  </si>
+  <si>
+    <t>England</t>
   </si>
 </sst>
 </file>
@@ -505,11 +511,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCCA43B-3F56-0941-9A80-D2A9636FEC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F7C392-630D-F64B-BA1C-C3689E0AAC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Vinst</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
   <si>
     <t>Frankrike</t>
   </si>
@@ -66,6 +63,18 @@
   </si>
   <si>
     <t>England</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Vinnare</t>
+  </si>
+  <si>
+    <t>Trea</t>
+  </si>
+  <si>
+    <t>Final</t>
   </si>
 </sst>
 </file>
@@ -452,20 +461,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{891B79A2-DBD9-2649-8A09-5F0D2D8A68DC}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
@@ -473,9 +484,11 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -483,13 +496,17 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -497,27 +514,72 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F7C392-630D-F64B-BA1C-C3689E0AAC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A11309-E32A-1340-863C-F41A0873E924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>Frankrike</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>Final</t>
+  </si>
+  <si>
+    <t>Spanien</t>
+  </si>
+  <si>
+    <t>Belgien</t>
   </si>
 </sst>
 </file>
@@ -565,12 +571,12 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A11309-E32A-1340-863C-F41A0873E924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A143259-78D9-CC40-AD2D-6B3A04A7EBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>Frankrike</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Belgien</t>
+  </si>
+  <si>
+    <t>Argentina</t>
   </si>
 </sst>
 </file>
@@ -581,7 +584,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A143259-78D9-CC40-AD2D-6B3A04A7EBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5F114B-88EC-0145-A2CA-1947098EB5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>Frankrike</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Argentina</t>
+  </si>
+  <si>
+    <t>Schweiz</t>
   </si>
 </sst>
 </file>
@@ -538,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -589,7 +592,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5F114B-88EC-0145-A2CA-1947098EB5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58873B22-7B80-BB4A-8CE4-C4BA60DF0D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Frankrike</t>
   </si>
@@ -546,6 +546,16 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58873B22-7B80-BB4A-8CE4-C4BA60DF0D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6790FD24-317A-564F-93AC-85F9820F0973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -551,12 +551,12 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6790FD24-317A-564F-93AC-85F9820F0973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CB3705-9969-474E-8A39-0F2821D26109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -511,7 +511,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CB3705-9969-474E-8A39-0F2821D26109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B74965-D78B-504A-861E-F9BC1A64911F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -517,7 +517,7 @@
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B74965-D78B-504A-861E-F9BC1A64911F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776C4062-06DF-B640-981F-D5AFB818D967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -529,7 +529,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">

--- a/Resultat.xlsx
+++ b/Resultat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ellabacklund/Claude_project/vm-tippning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776C4062-06DF-B640-981F-D5AFB818D967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA56723-E1B7-5340-A825-38A65A5670C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="15880" xr2:uid="{F9B9E0B2-0622-234A-8FBC-8B192F70E9B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>Frankrike</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>England</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
   <si>
     <t>Vinnare</t>
@@ -484,10 +481,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -499,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -508,16 +505,16 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -526,7 +523,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -546,7 +543,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -556,7 +553,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -587,22 +584,22 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
